--- a/tests/TC-08/results/timetable_all_departments_even.xlsx
+++ b/tests/TC-08/results/timetable_all_departments_even.xlsx
@@ -78,12 +78,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFDAB3"/>
-        <bgColor rgb="00FFDAB3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00E0E0E0"/>
         <bgColor rgb="00E0E0E0"/>
       </patternFill>
@@ -92,6 +86,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00C8E6C9"/>
         <bgColor rgb="00C8E6C9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFDAB3"/>
+        <bgColor rgb="00FFDAB3"/>
       </patternFill>
     </fill>
     <fill>
@@ -183,14 +183,14 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -201,10 +201,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
   </cellXfs>
@@ -809,21 +809,14 @@
       </c>
       <c r="C2" s="8" t="inlineStr"/>
       <c r="D2" s="8" t="inlineStr"/>
-      <c r="E2" s="9" t="inlineStr">
-        <is>
-          <t>CS163
-LEC
-Room: 102
-Dr. Vivekraj</t>
-        </is>
-      </c>
-      <c r="F2" s="10" t="n"/>
-      <c r="G2" s="10" t="n"/>
-      <c r="H2" s="11" t="n"/>
+      <c r="E2" s="8" t="inlineStr"/>
+      <c r="F2" s="8" t="inlineStr"/>
+      <c r="G2" s="8" t="inlineStr"/>
+      <c r="H2" s="8" t="inlineStr"/>
       <c r="I2" s="8" t="inlineStr"/>
       <c r="J2" s="8" t="inlineStr"/>
       <c r="K2" s="8" t="inlineStr"/>
-      <c r="L2" s="12" t="inlineStr">
+      <c r="L2" s="9" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
@@ -832,16 +825,9 @@
       <c r="N2" s="8" t="inlineStr"/>
       <c r="O2" s="8" t="inlineStr"/>
       <c r="P2" s="8" t="inlineStr"/>
-      <c r="Q2" s="13" t="inlineStr">
-        <is>
-          <t>MA163
-LEC
-Room: 101
-Dr. Anand</t>
-        </is>
-      </c>
-      <c r="R2" s="10" t="n"/>
-      <c r="S2" s="11" t="n"/>
+      <c r="Q2" s="8" t="inlineStr"/>
+      <c r="R2" s="8" t="inlineStr"/>
+      <c r="S2" s="8" t="inlineStr"/>
       <c r="T2" s="8" t="inlineStr"/>
       <c r="U2" s="7" t="inlineStr">
         <is>
@@ -869,32 +855,25 @@
       <c r="I3" s="8" t="inlineStr"/>
       <c r="J3" s="8" t="inlineStr"/>
       <c r="K3" s="8" t="inlineStr"/>
-      <c r="L3" s="12" t="inlineStr">
+      <c r="L3" s="9" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
       <c r="M3" s="8" t="inlineStr"/>
-      <c r="N3" s="13" t="inlineStr">
+      <c r="N3" s="10" t="inlineStr">
         <is>
           <t>MA163
-TUT
+LEC
 Room: 101
 Dr. Anand</t>
         </is>
       </c>
-      <c r="O3" s="9" t="inlineStr">
-        <is>
-          <t>CS163
-LAB
-Room: L101
-Dr. Vivekraj</t>
-        </is>
-      </c>
-      <c r="P3" s="10" t="n"/>
-      <c r="Q3" s="10" t="n"/>
-      <c r="R3" s="10" t="n"/>
-      <c r="S3" s="11" t="n"/>
+      <c r="O3" s="11" t="n"/>
+      <c r="P3" s="12" t="n"/>
+      <c r="Q3" s="8" t="inlineStr"/>
+      <c r="R3" s="8" t="inlineStr"/>
+      <c r="S3" s="8" t="inlineStr"/>
       <c r="T3" s="8" t="inlineStr"/>
       <c r="U3" s="7" t="inlineStr">
         <is>
@@ -917,27 +896,27 @@
       <c r="D4" s="8" t="inlineStr"/>
       <c r="E4" s="8" t="inlineStr"/>
       <c r="F4" s="8" t="inlineStr"/>
-      <c r="G4" s="8" t="inlineStr"/>
-      <c r="H4" s="8" t="inlineStr"/>
-      <c r="I4" s="8" t="inlineStr"/>
-      <c r="J4" s="8" t="inlineStr"/>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>MA163
+LEC
+Room: 101
+Dr. Anand</t>
+        </is>
+      </c>
+      <c r="H4" s="11" t="n"/>
+      <c r="I4" s="11" t="n"/>
+      <c r="J4" s="12" t="n"/>
       <c r="K4" s="8" t="inlineStr"/>
-      <c r="L4" s="12" t="inlineStr">
+      <c r="L4" s="9" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
       <c r="M4" s="8" t="inlineStr"/>
-      <c r="N4" s="9" t="inlineStr">
-        <is>
-          <t>CS163
-LEC
-Room: 102
-Dr. Vivekraj</t>
-        </is>
-      </c>
-      <c r="O4" s="10" t="n"/>
-      <c r="P4" s="11" t="n"/>
+      <c r="N4" s="8" t="inlineStr"/>
+      <c r="O4" s="8" t="inlineStr"/>
+      <c r="P4" s="8" t="inlineStr"/>
       <c r="Q4" s="8" t="inlineStr"/>
       <c r="R4" s="8" t="inlineStr"/>
       <c r="S4" s="8" t="inlineStr"/>
@@ -959,23 +938,30 @@
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr"/>
-      <c r="D5" s="8" t="inlineStr"/>
-      <c r="E5" s="8" t="inlineStr"/>
-      <c r="F5" s="8" t="inlineStr"/>
-      <c r="G5" s="13" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>CS163
+LAB
+Room: L102
+Dr. Vivekraj</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="n"/>
+      <c r="E5" s="11" t="n"/>
+      <c r="F5" s="12" t="n"/>
+      <c r="G5" s="8" t="inlineStr"/>
+      <c r="H5" s="10" t="inlineStr">
         <is>
           <t>MA163
-LEC
+TUT
 Room: 101
 Dr. Anand</t>
         </is>
       </c>
-      <c r="H5" s="10" t="n"/>
-      <c r="I5" s="10" t="n"/>
-      <c r="J5" s="11" t="n"/>
+      <c r="I5" s="11" t="n"/>
+      <c r="J5" s="12" t="n"/>
       <c r="K5" s="8" t="inlineStr"/>
-      <c r="L5" s="12" t="inlineStr">
+      <c r="L5" s="9" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
@@ -984,9 +970,16 @@
       <c r="N5" s="8" t="inlineStr"/>
       <c r="O5" s="8" t="inlineStr"/>
       <c r="P5" s="8" t="inlineStr"/>
-      <c r="Q5" s="8" t="inlineStr"/>
-      <c r="R5" s="8" t="inlineStr"/>
-      <c r="S5" s="8" t="inlineStr"/>
+      <c r="Q5" s="13" t="inlineStr">
+        <is>
+          <t>CS163
+LEC
+Room: 102
+Dr. Vivekraj</t>
+        </is>
+      </c>
+      <c r="R5" s="11" t="n"/>
+      <c r="S5" s="12" t="n"/>
       <c r="T5" s="8" t="inlineStr"/>
       <c r="U5" s="7" t="inlineStr">
         <is>
@@ -1005,8 +998,15 @@
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr"/>
-      <c r="D6" s="8" t="inlineStr"/>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>CS163
+LEC
+Room: 102
+Dr. Vivekraj</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="n"/>
       <c r="E6" s="8" t="inlineStr"/>
       <c r="F6" s="8" t="inlineStr"/>
       <c r="G6" s="8" t="inlineStr"/>
@@ -1014,7 +1014,7 @@
       <c r="I6" s="8" t="inlineStr"/>
       <c r="J6" s="8" t="inlineStr"/>
       <c r="K6" s="8" t="inlineStr"/>
-      <c r="L6" s="12" t="inlineStr">
+      <c r="L6" s="9" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
@@ -1129,12 +1129,13 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="O3:S3"/>
-    <mergeCell ref="N4:P4"/>
-    <mergeCell ref="G5:J5"/>
-    <mergeCell ref="E2:H2"/>
-    <mergeCell ref="Q2:S2"/>
+  <mergeCells count="6">
+    <mergeCell ref="Q5:S5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="G4:J4"/>
+    <mergeCell ref="H5:J5"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="N3:P3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1294,20 +1295,13 @@
       <c r="C2" s="8" t="inlineStr"/>
       <c r="D2" s="8" t="inlineStr"/>
       <c r="E2" s="8" t="inlineStr"/>
-      <c r="F2" s="9" t="inlineStr">
-        <is>
-          <t>CS163
-LEC
-Room: 101
-Dr. Hazra</t>
-        </is>
-      </c>
-      <c r="G2" s="10" t="n"/>
-      <c r="H2" s="10" t="n"/>
-      <c r="I2" s="11" t="n"/>
+      <c r="F2" s="8" t="inlineStr"/>
+      <c r="G2" s="8" t="inlineStr"/>
+      <c r="H2" s="8" t="inlineStr"/>
+      <c r="I2" s="8" t="inlineStr"/>
       <c r="J2" s="8" t="inlineStr"/>
       <c r="K2" s="8" t="inlineStr"/>
-      <c r="L2" s="12" t="inlineStr">
+      <c r="L2" s="9" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
@@ -1316,7 +1310,50 @@
       <c r="N2" s="8" t="inlineStr"/>
       <c r="O2" s="8" t="inlineStr"/>
       <c r="P2" s="8" t="inlineStr"/>
-      <c r="Q2" s="13" t="inlineStr">
+      <c r="Q2" s="8" t="inlineStr"/>
+      <c r="R2" s="8" t="inlineStr"/>
+      <c r="S2" s="8" t="inlineStr"/>
+      <c r="T2" s="8" t="inlineStr"/>
+      <c r="U2" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="40" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr"/>
+      <c r="D3" s="13" t="inlineStr">
+        <is>
+          <t>CS163
+LEC
+Room: 102
+Dr. Hazra</t>
+        </is>
+      </c>
+      <c r="E3" s="11" t="n"/>
+      <c r="F3" s="11" t="n"/>
+      <c r="G3" s="12" t="n"/>
+      <c r="H3" s="8" t="inlineStr"/>
+      <c r="I3" s="8" t="inlineStr"/>
+      <c r="J3" s="8" t="inlineStr"/>
+      <c r="K3" s="8" t="inlineStr"/>
+      <c r="L3" s="9" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M3" s="8" t="inlineStr"/>
+      <c r="N3" s="10" t="inlineStr">
         <is>
           <t>MA163
 LEC
@@ -1324,42 +1361,95 @@
 Dr. Anand</t>
         </is>
       </c>
-      <c r="R2" s="10" t="n"/>
-      <c r="S2" s="11" t="n"/>
-      <c r="T2" s="8" t="inlineStr"/>
-      <c r="U2" s="7" t="inlineStr">
+      <c r="O3" s="11" t="n"/>
+      <c r="P3" s="12" t="n"/>
+      <c r="Q3" s="8" t="inlineStr"/>
+      <c r="R3" s="8" t="inlineStr"/>
+      <c r="S3" s="8" t="inlineStr"/>
+      <c r="T3" s="8" t="inlineStr"/>
+      <c r="U3" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="40" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr"/>
-      <c r="D3" s="8" t="inlineStr"/>
-      <c r="E3" s="8" t="inlineStr"/>
-      <c r="F3" s="8" t="inlineStr"/>
-      <c r="G3" s="8" t="inlineStr"/>
-      <c r="H3" s="8" t="inlineStr"/>
-      <c r="I3" s="8" t="inlineStr"/>
-      <c r="J3" s="8" t="inlineStr"/>
-      <c r="K3" s="8" t="inlineStr"/>
-      <c r="L3" s="12" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr"/>
+      <c r="D4" s="8" t="inlineStr"/>
+      <c r="E4" s="8" t="inlineStr"/>
+      <c r="F4" s="8" t="inlineStr"/>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>MA163
+LEC
+Room: 101
+Dr. Anand</t>
+        </is>
+      </c>
+      <c r="H4" s="11" t="n"/>
+      <c r="I4" s="11" t="n"/>
+      <c r="J4" s="12" t="n"/>
+      <c r="K4" s="8" t="inlineStr"/>
+      <c r="L4" s="9" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
-      <c r="M3" s="8" t="inlineStr"/>
-      <c r="N3" s="13" t="inlineStr">
+      <c r="M4" s="8" t="inlineStr"/>
+      <c r="N4" s="13" t="inlineStr">
+        <is>
+          <t>CS163
+LEC
+Room: 102
+Dr. Hazra</t>
+        </is>
+      </c>
+      <c r="O4" s="11" t="n"/>
+      <c r="P4" s="12" t="n"/>
+      <c r="Q4" s="8" t="inlineStr"/>
+      <c r="R4" s="8" t="inlineStr"/>
+      <c r="S4" s="8" t="inlineStr"/>
+      <c r="T4" s="8" t="inlineStr"/>
+      <c r="U4" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>CS163
+LAB
+Room: L101
+Dr. Hazra</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="n"/>
+      <c r="E5" s="11" t="n"/>
+      <c r="F5" s="12" t="n"/>
+      <c r="G5" s="8" t="inlineStr"/>
+      <c r="H5" s="10" t="inlineStr">
         <is>
           <t>MA163
 TUT
@@ -1367,99 +1457,10 @@
 Dr. Anand</t>
         </is>
       </c>
-      <c r="O3" s="8" t="inlineStr"/>
-      <c r="P3" s="9" t="inlineStr">
-        <is>
-          <t>CS163
-LEC
-Room: 101
-Dr. Hazra</t>
-        </is>
-      </c>
-      <c r="Q3" s="10" t="n"/>
-      <c r="R3" s="11" t="n"/>
-      <c r="S3" s="8" t="inlineStr"/>
-      <c r="T3" s="8" t="inlineStr"/>
-      <c r="U3" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="40" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr"/>
-      <c r="D4" s="8" t="inlineStr"/>
-      <c r="E4" s="8" t="inlineStr"/>
-      <c r="F4" s="8" t="inlineStr"/>
-      <c r="G4" s="8" t="inlineStr"/>
-      <c r="H4" s="8" t="inlineStr"/>
-      <c r="I4" s="8" t="inlineStr"/>
-      <c r="J4" s="8" t="inlineStr"/>
-      <c r="K4" s="8" t="inlineStr"/>
-      <c r="L4" s="12" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M4" s="8" t="inlineStr"/>
-      <c r="N4" s="8" t="inlineStr"/>
-      <c r="O4" s="8" t="inlineStr"/>
-      <c r="P4" s="8" t="inlineStr"/>
-      <c r="Q4" s="8" t="inlineStr"/>
-      <c r="R4" s="9" t="inlineStr">
-        <is>
-          <t>CS163
-LAB
-Room: L101
-Dr. Hazra</t>
-        </is>
-      </c>
-      <c r="S4" s="10" t="n"/>
-      <c r="T4" s="11" t="n"/>
-      <c r="U4" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="40" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr"/>
-      <c r="D5" s="8" t="inlineStr"/>
-      <c r="E5" s="8" t="inlineStr"/>
-      <c r="F5" s="8" t="inlineStr"/>
-      <c r="G5" s="13" t="inlineStr">
-        <is>
-          <t>MA163
-LEC
-Room: 101
-Dr. Anand</t>
-        </is>
-      </c>
-      <c r="H5" s="10" t="n"/>
-      <c r="I5" s="10" t="n"/>
-      <c r="J5" s="11" t="n"/>
+      <c r="I5" s="11" t="n"/>
+      <c r="J5" s="12" t="n"/>
       <c r="K5" s="8" t="inlineStr"/>
-      <c r="L5" s="12" t="inlineStr">
+      <c r="L5" s="9" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
@@ -1498,7 +1499,7 @@
       <c r="I6" s="8" t="inlineStr"/>
       <c r="J6" s="8" t="inlineStr"/>
       <c r="K6" s="8" t="inlineStr"/>
-      <c r="L6" s="12" t="inlineStr">
+      <c r="L6" s="9" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
@@ -1580,7 +1581,7 @@
       </c>
       <c r="F12" s="16" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
     </row>
@@ -1613,12 +1614,13 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="R4:T4"/>
-    <mergeCell ref="G5:J5"/>
-    <mergeCell ref="P3:R3"/>
-    <mergeCell ref="Q2:S2"/>
+  <mergeCells count="6">
+    <mergeCell ref="D3:G3"/>
+    <mergeCell ref="G4:J4"/>
+    <mergeCell ref="H5:J5"/>
+    <mergeCell ref="N4:P4"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="N3:P3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1630,7 +1632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1682,22 +1684,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Dr. Vivekraj</t>
+          <t>Dr. Anand</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1707,7 +1709,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>CS163</t>
+          <t>MA163</t>
         </is>
       </c>
     </row>
@@ -1718,13 +1720,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1754,13 +1756,13 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>5</v>
+      </c>
+      <c r="C4" t="n">
         <v>3</v>
       </c>
-      <c r="C4" t="n">
-        <v>15</v>
-      </c>
       <c r="D4" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1769,7 +1771,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>L101</t>
+          <t>L102</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1790,32 +1792,32 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C5" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dr. Vivekraj</t>
+          <t>Dr. Anand</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>CS163</t>
+          <t>MA163</t>
         </is>
       </c>
     </row>
@@ -1829,19 +1831,19 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dr. Anand</t>
+          <t>Dr. Vivekraj</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1851,33 +1853,33 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>MA163</t>
+          <t>CS163</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CSE_2_B</t>
+          <t>CSE_2_A</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dr. Hazra</t>
+          <t>Dr. Vivekraj</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1898,22 +1900,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dr. Anand</t>
+          <t>Dr. Hazra</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1923,7 +1925,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>MA163</t>
+          <t>CS163</t>
         </is>
       </c>
     </row>
@@ -1937,14 +1939,14 @@
         <v>3</v>
       </c>
       <c r="C9" t="n">
+        <v>14</v>
+      </c>
+      <c r="D9" t="n">
         <v>16</v>
       </c>
-      <c r="D9" t="n">
-        <v>18</v>
-      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dr. Hazra</t>
+          <t>Dr. Anand</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1959,7 +1961,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>CS163</t>
+          <t>MA163</t>
         </is>
       </c>
     </row>
@@ -1973,29 +1975,29 @@
         <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dr. Hazra</t>
+          <t>Dr. Anand</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>L101</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>LAB</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>CS163</t>
+          <t>MA163</t>
         </is>
       </c>
     </row>
@@ -2006,30 +2008,102 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C11" t="n">
+        <v>14</v>
+      </c>
+      <c r="D11" t="n">
+        <v>16</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Dr. Hazra</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>LEC</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>CS163</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CSE_2_B</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
         <v>5</v>
       </c>
-      <c r="C11" t="n">
-        <v>7</v>
-      </c>
-      <c r="D11" t="n">
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>6</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Dr. Hazra</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>L101</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>LAB</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>CS163</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CSE_2_B</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" t="n">
+        <v>8</v>
+      </c>
+      <c r="D13" t="n">
         <v>10</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>Dr. Anand</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>LEC</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
         <is>
           <t>MA163</t>
         </is>

--- a/tests/TC-08/results/timetable_all_departments_even.xlsx
+++ b/tests/TC-08/results/timetable_all_departments_even.xlsx
@@ -78,14 +78,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E0E0E0"/>
-        <bgColor rgb="00E0E0E0"/>
+        <fgColor rgb="00C8E6C9"/>
+        <bgColor rgb="00C8E6C9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C8E6C9"/>
-        <bgColor rgb="00C8E6C9"/>
+        <fgColor rgb="00E0E0E0"/>
+        <bgColor rgb="00E0E0E0"/>
       </patternFill>
     </fill>
     <fill>
@@ -183,14 +183,14 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -204,7 +204,7 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
   </cellXfs>
@@ -812,11 +812,18 @@
       <c r="E2" s="8" t="inlineStr"/>
       <c r="F2" s="8" t="inlineStr"/>
       <c r="G2" s="8" t="inlineStr"/>
-      <c r="H2" s="8" t="inlineStr"/>
-      <c r="I2" s="8" t="inlineStr"/>
-      <c r="J2" s="8" t="inlineStr"/>
+      <c r="H2" s="9" t="inlineStr">
+        <is>
+          <t>MA163
+TUT
+Room: 101
+Dr. Anand</t>
+        </is>
+      </c>
+      <c r="I2" s="10" t="n"/>
+      <c r="J2" s="11" t="n"/>
       <c r="K2" s="8" t="inlineStr"/>
-      <c r="L2" s="9" t="inlineStr">
+      <c r="L2" s="12" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
@@ -824,9 +831,16 @@
       <c r="M2" s="8" t="inlineStr"/>
       <c r="N2" s="8" t="inlineStr"/>
       <c r="O2" s="8" t="inlineStr"/>
-      <c r="P2" s="8" t="inlineStr"/>
-      <c r="Q2" s="8" t="inlineStr"/>
-      <c r="R2" s="8" t="inlineStr"/>
+      <c r="P2" s="13" t="inlineStr">
+        <is>
+          <t>CS163
+LEC
+Room: 102
+Dr. Vivekraj</t>
+        </is>
+      </c>
+      <c r="Q2" s="10" t="n"/>
+      <c r="R2" s="11" t="n"/>
       <c r="S2" s="8" t="inlineStr"/>
       <c r="T2" s="8" t="inlineStr"/>
       <c r="U2" s="7" t="inlineStr">
@@ -848,20 +862,7 @@
       </c>
       <c r="C3" s="8" t="inlineStr"/>
       <c r="D3" s="8" t="inlineStr"/>
-      <c r="E3" s="8" t="inlineStr"/>
-      <c r="F3" s="8" t="inlineStr"/>
-      <c r="G3" s="8" t="inlineStr"/>
-      <c r="H3" s="8" t="inlineStr"/>
-      <c r="I3" s="8" t="inlineStr"/>
-      <c r="J3" s="8" t="inlineStr"/>
-      <c r="K3" s="8" t="inlineStr"/>
-      <c r="L3" s="9" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M3" s="8" t="inlineStr"/>
-      <c r="N3" s="10" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>MA163
 LEC
@@ -869,8 +870,21 @@
 Dr. Anand</t>
         </is>
       </c>
-      <c r="O3" s="11" t="n"/>
-      <c r="P3" s="12" t="n"/>
+      <c r="F3" s="10" t="n"/>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="11" t="n"/>
+      <c r="I3" s="8" t="inlineStr"/>
+      <c r="J3" s="8" t="inlineStr"/>
+      <c r="K3" s="8" t="inlineStr"/>
+      <c r="L3" s="12" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M3" s="8" t="inlineStr"/>
+      <c r="N3" s="8" t="inlineStr"/>
+      <c r="O3" s="8" t="inlineStr"/>
+      <c r="P3" s="8" t="inlineStr"/>
       <c r="Q3" s="8" t="inlineStr"/>
       <c r="R3" s="8" t="inlineStr"/>
       <c r="S3" s="8" t="inlineStr"/>
@@ -892,11 +906,17 @@
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr"/>
-      <c r="D4" s="8" t="inlineStr"/>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>CS163
+LEC
+Room: 102
+Dr. Vivekraj</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="n"/>
       <c r="E4" s="8" t="inlineStr"/>
-      <c r="F4" s="8" t="inlineStr"/>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="F4" s="9" t="inlineStr">
         <is>
           <t>MA163
 LEC
@@ -904,11 +924,12 @@
 Dr. Anand</t>
         </is>
       </c>
-      <c r="H4" s="11" t="n"/>
+      <c r="G4" s="10" t="n"/>
+      <c r="H4" s="10" t="n"/>
       <c r="I4" s="11" t="n"/>
-      <c r="J4" s="12" t="n"/>
+      <c r="J4" s="8" t="inlineStr"/>
       <c r="K4" s="8" t="inlineStr"/>
-      <c r="L4" s="9" t="inlineStr">
+      <c r="L4" s="12" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
@@ -938,7 +959,46 @@
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr"/>
+      <c r="D5" s="8" t="inlineStr"/>
+      <c r="E5" s="8" t="inlineStr"/>
+      <c r="F5" s="8" t="inlineStr"/>
+      <c r="G5" s="8" t="inlineStr"/>
+      <c r="H5" s="8" t="inlineStr"/>
+      <c r="I5" s="8" t="inlineStr"/>
+      <c r="J5" s="8" t="inlineStr"/>
+      <c r="K5" s="8" t="inlineStr"/>
+      <c r="L5" s="12" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M5" s="8" t="inlineStr"/>
+      <c r="N5" s="8" t="inlineStr"/>
+      <c r="O5" s="8" t="inlineStr"/>
+      <c r="P5" s="8" t="inlineStr"/>
+      <c r="Q5" s="8" t="inlineStr"/>
+      <c r="R5" s="8" t="inlineStr"/>
+      <c r="S5" s="8" t="inlineStr"/>
+      <c r="T5" s="8" t="inlineStr"/>
+      <c r="U5" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>CS163
 LAB
@@ -946,75 +1006,15 @@
 Dr. Vivekraj</t>
         </is>
       </c>
-      <c r="D5" s="11" t="n"/>
-      <c r="E5" s="11" t="n"/>
-      <c r="F5" s="12" t="n"/>
-      <c r="G5" s="8" t="inlineStr"/>
-      <c r="H5" s="10" t="inlineStr">
-        <is>
-          <t>MA163
-TUT
-Room: 101
-Dr. Anand</t>
-        </is>
-      </c>
-      <c r="I5" s="11" t="n"/>
-      <c r="J5" s="12" t="n"/>
-      <c r="K5" s="8" t="inlineStr"/>
-      <c r="L5" s="9" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M5" s="8" t="inlineStr"/>
-      <c r="N5" s="8" t="inlineStr"/>
-      <c r="O5" s="8" t="inlineStr"/>
-      <c r="P5" s="8" t="inlineStr"/>
-      <c r="Q5" s="13" t="inlineStr">
-        <is>
-          <t>CS163
-LEC
-Room: 102
-Dr. Vivekraj</t>
-        </is>
-      </c>
-      <c r="R5" s="11" t="n"/>
-      <c r="S5" s="12" t="n"/>
-      <c r="T5" s="8" t="inlineStr"/>
-      <c r="U5" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="40" customHeight="1">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Friday</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C6" s="13" t="inlineStr">
-        <is>
-          <t>CS163
-LEC
-Room: 102
-Dr. Vivekraj</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="n"/>
-      <c r="E6" s="8" t="inlineStr"/>
-      <c r="F6" s="8" t="inlineStr"/>
+      <c r="D6" s="10" t="n"/>
+      <c r="E6" s="10" t="n"/>
+      <c r="F6" s="11" t="n"/>
       <c r="G6" s="8" t="inlineStr"/>
       <c r="H6" s="8" t="inlineStr"/>
       <c r="I6" s="8" t="inlineStr"/>
       <c r="J6" s="8" t="inlineStr"/>
       <c r="K6" s="8" t="inlineStr"/>
-      <c r="L6" s="9" t="inlineStr">
+      <c r="L6" s="12" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
@@ -1130,12 +1130,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="Q5:S5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="G4:J4"/>
-    <mergeCell ref="H5:J5"/>
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="E3:H3"/>
+    <mergeCell ref="P2:R2"/>
+    <mergeCell ref="F4:I4"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="C4:D4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1297,11 +1297,18 @@
       <c r="E2" s="8" t="inlineStr"/>
       <c r="F2" s="8" t="inlineStr"/>
       <c r="G2" s="8" t="inlineStr"/>
-      <c r="H2" s="8" t="inlineStr"/>
-      <c r="I2" s="8" t="inlineStr"/>
-      <c r="J2" s="8" t="inlineStr"/>
+      <c r="H2" s="9" t="inlineStr">
+        <is>
+          <t>MA163
+TUT
+Room: 101
+Dr. Anand</t>
+        </is>
+      </c>
+      <c r="I2" s="10" t="n"/>
+      <c r="J2" s="11" t="n"/>
       <c r="K2" s="8" t="inlineStr"/>
-      <c r="L2" s="9" t="inlineStr">
+      <c r="L2" s="12" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
@@ -1332,28 +1339,8 @@
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr"/>
-      <c r="D3" s="13" t="inlineStr">
-        <is>
-          <t>CS163
-LEC
-Room: 102
-Dr. Hazra</t>
-        </is>
-      </c>
-      <c r="E3" s="11" t="n"/>
-      <c r="F3" s="11" t="n"/>
-      <c r="G3" s="12" t="n"/>
-      <c r="H3" s="8" t="inlineStr"/>
-      <c r="I3" s="8" t="inlineStr"/>
-      <c r="J3" s="8" t="inlineStr"/>
-      <c r="K3" s="8" t="inlineStr"/>
-      <c r="L3" s="9" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M3" s="8" t="inlineStr"/>
-      <c r="N3" s="10" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr"/>
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>MA163
 LEC
@@ -1361,11 +1348,31 @@
 Dr. Anand</t>
         </is>
       </c>
-      <c r="O3" s="11" t="n"/>
-      <c r="P3" s="12" t="n"/>
-      <c r="Q3" s="8" t="inlineStr"/>
-      <c r="R3" s="8" t="inlineStr"/>
-      <c r="S3" s="8" t="inlineStr"/>
+      <c r="F3" s="10" t="n"/>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="11" t="n"/>
+      <c r="I3" s="8" t="inlineStr"/>
+      <c r="J3" s="8" t="inlineStr"/>
+      <c r="K3" s="8" t="inlineStr"/>
+      <c r="L3" s="12" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M3" s="8" t="inlineStr"/>
+      <c r="N3" s="8" t="inlineStr"/>
+      <c r="O3" s="13" t="inlineStr">
+        <is>
+          <t>CS163
+LAB
+Room: L102
+Dr. Hazra</t>
+        </is>
+      </c>
+      <c r="P3" s="10" t="n"/>
+      <c r="Q3" s="10" t="n"/>
+      <c r="R3" s="10" t="n"/>
+      <c r="S3" s="11" t="n"/>
       <c r="T3" s="8" t="inlineStr"/>
       <c r="U3" s="7" t="inlineStr">
         <is>
@@ -1387,8 +1394,7 @@
       <c r="C4" s="8" t="inlineStr"/>
       <c r="D4" s="8" t="inlineStr"/>
       <c r="E4" s="8" t="inlineStr"/>
-      <c r="F4" s="8" t="inlineStr"/>
-      <c r="G4" s="10" t="inlineStr">
+      <c r="F4" s="9" t="inlineStr">
         <is>
           <t>MA163
 LEC
@@ -1396,26 +1402,20 @@
 Dr. Anand</t>
         </is>
       </c>
-      <c r="H4" s="11" t="n"/>
+      <c r="G4" s="10" t="n"/>
+      <c r="H4" s="10" t="n"/>
       <c r="I4" s="11" t="n"/>
-      <c r="J4" s="12" t="n"/>
+      <c r="J4" s="8" t="inlineStr"/>
       <c r="K4" s="8" t="inlineStr"/>
-      <c r="L4" s="9" t="inlineStr">
+      <c r="L4" s="12" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
       <c r="M4" s="8" t="inlineStr"/>
-      <c r="N4" s="13" t="inlineStr">
-        <is>
-          <t>CS163
-LEC
-Room: 102
-Dr. Hazra</t>
-        </is>
-      </c>
-      <c r="O4" s="11" t="n"/>
-      <c r="P4" s="12" t="n"/>
+      <c r="N4" s="8" t="inlineStr"/>
+      <c r="O4" s="8" t="inlineStr"/>
+      <c r="P4" s="8" t="inlineStr"/>
       <c r="Q4" s="8" t="inlineStr"/>
       <c r="R4" s="8" t="inlineStr"/>
       <c r="S4" s="8" t="inlineStr"/>
@@ -1440,27 +1440,20 @@
       <c r="C5" s="13" t="inlineStr">
         <is>
           <t>CS163
-LAB
-Room: L101
+LEC
+Room: 102
 Dr. Hazra</t>
         </is>
       </c>
       <c r="D5" s="11" t="n"/>
-      <c r="E5" s="11" t="n"/>
-      <c r="F5" s="12" t="n"/>
+      <c r="E5" s="8" t="inlineStr"/>
+      <c r="F5" s="8" t="inlineStr"/>
       <c r="G5" s="8" t="inlineStr"/>
-      <c r="H5" s="10" t="inlineStr">
-        <is>
-          <t>MA163
-TUT
-Room: 101
-Dr. Anand</t>
-        </is>
-      </c>
-      <c r="I5" s="11" t="n"/>
-      <c r="J5" s="12" t="n"/>
+      <c r="H5" s="8" t="inlineStr"/>
+      <c r="I5" s="8" t="inlineStr"/>
+      <c r="J5" s="8" t="inlineStr"/>
       <c r="K5" s="8" t="inlineStr"/>
-      <c r="L5" s="9" t="inlineStr">
+      <c r="L5" s="12" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
@@ -1499,15 +1492,22 @@
       <c r="I6" s="8" t="inlineStr"/>
       <c r="J6" s="8" t="inlineStr"/>
       <c r="K6" s="8" t="inlineStr"/>
-      <c r="L6" s="9" t="inlineStr">
+      <c r="L6" s="12" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
       <c r="M6" s="8" t="inlineStr"/>
-      <c r="N6" s="8" t="inlineStr"/>
-      <c r="O6" s="8" t="inlineStr"/>
-      <c r="P6" s="8" t="inlineStr"/>
+      <c r="N6" s="13" t="inlineStr">
+        <is>
+          <t>CS163
+LEC
+Room: 102
+Dr. Hazra</t>
+        </is>
+      </c>
+      <c r="O6" s="10" t="n"/>
+      <c r="P6" s="11" t="n"/>
       <c r="Q6" s="8" t="inlineStr"/>
       <c r="R6" s="8" t="inlineStr"/>
       <c r="S6" s="8" t="inlineStr"/>
@@ -1615,12 +1615,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="D3:G3"/>
-    <mergeCell ref="G4:J4"/>
-    <mergeCell ref="H5:J5"/>
-    <mergeCell ref="N4:P4"/>
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="N3:P3"/>
+    <mergeCell ref="O3:S3"/>
+    <mergeCell ref="E3:H3"/>
+    <mergeCell ref="F4:I4"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="N6:P6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1684,13 +1684,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1720,22 +1720,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Dr. Anand</t>
+          <t>Dr. Vivekraj</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>MA163</t>
+          <t>CS163</t>
         </is>
       </c>
     </row>
@@ -1756,32 +1756,32 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="n">
         <v>5</v>
       </c>
-      <c r="C4" t="n">
-        <v>3</v>
-      </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dr. Vivekraj</t>
+          <t>Dr. Anand</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>L102</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>LAB</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>CS163</t>
+          <t>MA163</t>
         </is>
       </c>
     </row>
@@ -1792,32 +1792,32 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dr. Anand</t>
+          <t>Dr. Vivekraj</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>MA163</t>
+          <t>CS163</t>
         </is>
       </c>
     </row>
@@ -1828,22 +1828,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dr. Vivekraj</t>
+          <t>Dr. Anand</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>CS163</t>
+          <t>MA163</t>
         </is>
       </c>
     </row>
@@ -1870,7 +1870,7 @@
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>L102</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>LAB</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1900,32 +1900,32 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dr. Hazra</t>
+          <t>Dr. Anand</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>CS163</t>
+          <t>MA163</t>
         </is>
       </c>
     </row>
@@ -1939,10 +1939,10 @@
         <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1972,32 +1972,32 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dr. Anand</t>
+          <t>Dr. Hazra</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>L102</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>LAB</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>MA163</t>
+          <t>CS163</t>
         </is>
       </c>
     </row>
@@ -2011,19 +2011,19 @@
         <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dr. Hazra</t>
+          <t>Dr. Anand</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>CS163</t>
+          <t>MA163</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2050,7 @@
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -2059,12 +2059,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>L101</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>LAB</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -2080,32 +2080,32 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dr. Anand</t>
+          <t>Dr. Hazra</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>102</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>LEC</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>MA163</t>
+          <t>CS163</t>
         </is>
       </c>
     </row>
